--- a/Intro_files/Checklisten.xlsx
+++ b/Intro_files/Checklisten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raidlp21\ucloud\Lehre\Personal Coaching Script\PersonalCoaching_Script\Intro_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paedd\OneDrive\Documents\GitHub\PersonalCoaching_Script\Intro_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2FA892-D9C1-4846-9497-ED7B871C1782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCE4AEC-0976-4E4D-93B6-90D050F4C17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{1F4A27A2-B6F2-4DE6-9482-90020ABE8025}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{1F4A27A2-B6F2-4DE6-9482-90020ABE8025}"/>
   </bookViews>
   <sheets>
     <sheet name="Semester_Seminar" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="75">
   <si>
     <t>X</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Check-in mit Klienten</t>
   </si>
   <si>
-    <t>Was kann ich tun damit ich locker und offen in die Einheit gehen kann?</t>
-  </si>
-  <si>
     <t>Selbst Ceck-in</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
     <t>Materialien bereit</t>
   </si>
   <si>
-    <t>klare Zielsetzung für die Einheit; Trainingsplan vorbereitet; Zeit für Akutes eingeplant; Zeit für Organisation eingeplant</t>
-  </si>
-  <si>
     <t>Stunde vorbereitet</t>
   </si>
   <si>
@@ -206,9 +200,6 @@
     <t>Letzte Coachingeinheit</t>
   </si>
   <si>
-    <t>Führe eine Supervision bei erfahrenen Personal Coaches durch</t>
-  </si>
-  <si>
     <t>Semesterende</t>
   </si>
   <si>
@@ -224,9 +215,6 @@
     <t>8.EH</t>
   </si>
   <si>
-    <t>Suche dir eine Supervisionsstelle bei erfahrenen Personal Coaches und Vereinbare einen Termin</t>
-  </si>
-  <si>
     <t>6EH</t>
   </si>
   <si>
@@ -258,6 +246,24 @@
   </si>
   <si>
     <t>Checkbox</t>
+  </si>
+  <si>
+    <t>3.EH</t>
+  </si>
+  <si>
+    <t>Prüfe die Beurteilungskriterien und Teilleistungen. Ist dir alles klar? Möchtest du neue Regelvorschläge oder Änderungen diskutieren?</t>
+  </si>
+  <si>
+    <t>Suche dir eine Hospitationsstelle bei erfahrenen Personal Coaches und Vereinbare einen Termin</t>
+  </si>
+  <si>
+    <t>Führe eine Hospitation bei erfahrenen Personal Coaches durch</t>
+  </si>
+  <si>
+    <t>Klare Zielsetzung für die Einheit; Trainingsplan vorbereitet; Zeit für Akutes eingeplant; Zeit für Organisation eingeplant</t>
+  </si>
+  <si>
+    <t>Was kann ich tun, damit ich locker und offen in die Einheit gehen kann?</t>
   </si>
 </sst>
 </file>
@@ -523,9 +529,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -544,215 +547,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -1149,130 +959,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEAFF3E6-FB39-41BB-8CF4-CB5D6130042E}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.28515625" style="1" customWidth="1"/>
-    <col min="3" max="22" width="7.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.26953125" style="1" customWidth="1"/>
+    <col min="3" max="22" width="7.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>66</v>
+    <row r="3" spans="1:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>64</v>
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>62</v>
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>60</v>
+    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>58</v>
+    <row r="7" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>57</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>56</v>
+    <row r="8" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>54</v>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C10">
-    <cfRule type="containsText" dxfId="35" priority="9" operator="containsText" text="X">
+  <conditionalFormatting sqref="C2:C11">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",C2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="10" operator="containsText" text="✓">
+    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="✓">
       <formula>NOT(ISERROR(SEARCH("✓",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1285,7 +1106,7 @@
           <x14:formula1>
             <xm:f>Background!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C10</xm:sqref>
+          <xm:sqref>C2:C11</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1296,80 +1117,80 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7329866-2490-4F24-8B73-AB5726E760D3}">
   <dimension ref="A1:U5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.28515625" style="1" customWidth="1"/>
-    <col min="2" max="21" width="7.28515625" customWidth="1"/>
+    <col min="1" max="1" width="65.26953125" style="1" customWidth="1"/>
+    <col min="2" max="21" width="7.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>50</v>
+    <row r="1" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>48</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U1" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>0</v>
@@ -1432,9 +1253,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>31</v>
+    <row r="3" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>0</v>
@@ -1497,9 +1318,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>30</v>
+    <row r="4" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>0</v>
@@ -1562,9 +1383,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>29</v>
+    <row r="5" spans="1:21" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>0</v>
@@ -1628,20 +1449,12 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:U1">
-    <cfRule type="containsText" dxfId="25" priority="11" operator="containsText" text="X">
+  <conditionalFormatting sqref="B1:U5">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="12" operator="containsText" text="✓">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="✓">
       <formula>NOT(ISERROR(SEARCH("✓",B1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:U5">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH("X",B2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="✓">
-      <formula>NOT(ISERROR(SEARCH("✓",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1664,37 +1477,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD966791-7C85-4644-B85B-04EAAD344615}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.28515625" style="1" customWidth="1"/>
-    <col min="3" max="22" width="7.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.26953125" style="1" customWidth="1"/>
+    <col min="3" max="22" width="7.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="12"/>
+    <row r="1" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="23"/>
       <c r="C1" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>0</v>
@@ -1709,12 +1522,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>0</v>
@@ -1729,12 +1542,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>0</v>
@@ -1749,12 +1562,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>0</v>
@@ -1769,12 +1582,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>0</v>
@@ -1789,7 +1602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
@@ -1809,7 +1622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>10</v>
       </c>
@@ -1829,7 +1642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
@@ -1849,7 +1662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>6</v>
       </c>
@@ -1869,7 +1682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>4</v>
       </c>
@@ -1889,7 +1702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="24.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
         <v>2</v>
       </c>
@@ -1909,31 +1722,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="12"/>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="A14" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="23"/>
       <c r="C14" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>0</v>
@@ -1948,12 +1761,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>0</v>
@@ -1968,12 +1781,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>0</v>
@@ -1988,12 +1801,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>0</v>
@@ -2008,12 +1821,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>0</v>
@@ -2028,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>12</v>
       </c>
@@ -2048,7 +1861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>10</v>
       </c>
@@ -2068,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>8</v>
       </c>
@@ -2088,7 +1901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>6</v>
       </c>
@@ -2108,7 +1921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>4</v>
       </c>
@@ -2128,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
         <v>2</v>
       </c>
@@ -2153,36 +1966,20 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1:F1">
-    <cfRule type="containsText" dxfId="13" priority="11" operator="containsText" text="X">
+  <conditionalFormatting sqref="C1:F12">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="✓">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="✓">
       <formula>NOT(ISERROR(SEARCH("✓",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:F14">
-    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="X">
+  <conditionalFormatting sqref="C14:F25">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",C14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="✓">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="✓">
       <formula>NOT(ISERROR(SEARCH("✓",C14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:F12">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH("X",C2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="✓">
-      <formula>NOT(ISERROR(SEARCH("✓",C2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C15:F25">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="X">
-      <formula>NOT(ISERROR(SEARCH("X",C15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="✓">
-      <formula>NOT(ISERROR(SEARCH("✓",C15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -2205,23 +2002,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAB527A-3846-4551-94DD-38628DD9F591}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="20" t="s">
         <v>0</v>
       </c>
     </row>
